--- a/sheets/대금율보/검수/어디로 갈거나.xlsx
+++ b/sheets/대금율보/검수/어디로 갈거나.xlsx
@@ -4410,8 +4410,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳フ
-‹</t>
+          <t xml:space="preserve">湳フ</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -4428,8 +4427,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳フ
-‹</t>
+          <t xml:space="preserve">湳フ</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
@@ -4446,8 +4444,7 @@
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳フ
-‹</t>
+          <t xml:space="preserve">湳フ</t>
         </is>
       </c>
       <c r="K8" s="24" t="inlineStr">
@@ -4465,8 +4462,7 @@
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="O8" s="24"/>

--- a/sheets/대금율보/검수/어디로 갈거나.xlsx
+++ b/sheets/대금율보/검수/어디로 갈거나.xlsx
@@ -4024,28 +4024,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4898,6 +4898,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>